--- a/public/exports-from-60-with-coowners/26696348.xlsx
+++ b/public/exports-from-60-with-coowners/26696348.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033111</t>
+          <t xml:space="preserve">200033151</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033702</t>
+          <t xml:space="preserve">200033703</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">

--- a/public/exports-from-60-with-coowners/26696348.xlsx
+++ b/public/exports-from-60-with-coowners/26696348.xlsx
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedningestræde 6</t>
+          <t xml:space="preserve">Ny Østergade 55</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405093</t>
+          <t xml:space="preserve">5405393</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -17685,11 +17685,11 @@
         </is>
       </c>
       <c r="J236">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033712</t>
+          <t xml:space="preserve">200033705</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Østergade 55</t>
+          <t xml:space="preserve">Ny Østergade 63</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405393</t>
+          <t xml:space="preserve">5405404</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033705</t>
+          <t xml:space="preserve">200033703</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Østergade 63</t>
+          <t xml:space="preserve">Søndre Alle 2A</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405404</t>
+          <t xml:space="preserve">5405178</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,11 +17835,11 @@
         </is>
       </c>
       <c r="J238">
-        <v>92</v>
+        <v>238</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033703</t>
+          <t xml:space="preserve">200033707</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 2A</t>
+          <t xml:space="preserve">Østergade 50</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405178</t>
+          <t xml:space="preserve">5405374</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -17910,11 +17910,11 @@
         </is>
       </c>
       <c r="J239">
-        <v>238</v>
+        <v>478</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033707</t>
+          <t xml:space="preserve">200033718</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 50</t>
+          <t xml:space="preserve">Sankt Mortens Gade 33</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405374</t>
+          <t xml:space="preserve">5405624</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="J240">
-        <v>478</v>
+        <v>1065</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033718</t>
+          <t xml:space="preserve">200034925</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-08-05</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Mortens Gade 33</t>
+          <t xml:space="preserve">Ullasvej 5</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405624</t>
+          <t xml:space="preserve">8341351</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -18060,11 +18060,11 @@
         </is>
       </c>
       <c r="J241">
-        <v>1065</v>
+        <v>455</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034925</t>
+          <t xml:space="preserve">200034911</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 5</t>
+          <t xml:space="preserve">Bellmansvej 22</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,15 +18131,15 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J242">
-        <v>455</v>
+        <v>103</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034911</t>
+          <t xml:space="preserve">200035071</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-05</t>
+          <t xml:space="preserve">2020-08-10</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bellmansvej 22</t>
+          <t xml:space="preserve">Bellmansvej 24</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18206,15 +18206,15 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J243">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035071</t>
+          <t xml:space="preserve">200035073</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18266,40 +18266,40 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bellmansvej 24</t>
+          <t xml:space="preserve">Kirkestræde 28</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341351</t>
+          <t xml:space="preserve">5402184</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035073</t>
+          <t xml:space="preserve">200035093</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-10</t>
+          <t xml:space="preserve">2020-08-11</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,35 +18341,35 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 28</t>
+          <t xml:space="preserve">Ullasvej 43</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402184</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="J245">
-        <v>224</v>
+        <v>1163</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035093</t>
+          <t xml:space="preserve">200035122</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 43</t>
+          <t xml:space="preserve">Helsevej 4</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18431,15 +18431,15 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J246">
-        <v>1163</v>
+        <v>432</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035122</t>
+          <t xml:space="preserve">200035251</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-11</t>
+          <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helsevej 4</t>
+          <t xml:space="preserve">Sagavej 19</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,20 +18501,20 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5411731</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J247">
-        <v>432</v>
+        <v>392</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035251</t>
+          <t xml:space="preserve">200035250</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18566,17 +18566,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sagavej 19</t>
+          <t xml:space="preserve">Pedersker Hovedgade 46</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411731</t>
+          <t xml:space="preserve">5154845</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,21 +18585,21 @@
         </is>
       </c>
       <c r="J248">
-        <v>392</v>
+        <v>542</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035229</t>
+          <t xml:space="preserve">200035679</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-13</t>
+          <t xml:space="preserve">2020-08-23</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildestræde 14A</t>
+          <t xml:space="preserve">Kirkestræde 32</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402422</t>
+          <t xml:space="preserve">5402188</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -18660,11 +18660,11 @@
         </is>
       </c>
       <c r="J249">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035312</t>
+          <t xml:space="preserve">200035749</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-15</t>
+          <t xml:space="preserve">2020-08-24</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,30 +18716,30 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedersker Hovedgade 46</t>
+          <t xml:space="preserve">Lindevej 5B</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5154845</t>
+          <t xml:space="preserve">288461</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J250">
-        <v>542</v>
+        <v>206</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035679</t>
+          <t xml:space="preserve">200035850</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-23</t>
+          <t xml:space="preserve">2020-08-26</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 32</t>
+          <t xml:space="preserve">Nørregade 46A</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402188</t>
+          <t xml:space="preserve">5403077</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -18810,11 +18810,11 @@
         </is>
       </c>
       <c r="J251">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035749</t>
+          <t xml:space="preserve">200035847</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-24</t>
+          <t xml:space="preserve">2020-08-26</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5B</t>
+          <t xml:space="preserve">Skippergade 8</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,20 +18876,20 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">288461</t>
+          <t xml:space="preserve">7796420</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J252">
-        <v>206</v>
+        <v>342</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035850</t>
+          <t xml:space="preserve">200035849</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18941,17 +18941,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 46A</t>
+          <t xml:space="preserve">Storegade 24</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403077</t>
+          <t xml:space="preserve">5413572</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -18960,11 +18960,11 @@
         </is>
       </c>
       <c r="J253">
-        <v>205</v>
+        <v>501</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035847</t>
+          <t xml:space="preserve">200035928</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-26</t>
+          <t xml:space="preserve">2020-08-27</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,17 +19016,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skippergade 8</t>
+          <t xml:space="preserve">Aasen 13</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">7796420</t>
+          <t xml:space="preserve">5402857</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -19035,11 +19035,11 @@
         </is>
       </c>
       <c r="J254">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035849</t>
+          <t xml:space="preserve">200036023</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-26</t>
+          <t xml:space="preserve">2020-08-30</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,17 +19091,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 24</t>
+          <t xml:space="preserve">Aasen 49A</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413572</t>
+          <t xml:space="preserve">5402786</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -19110,11 +19110,11 @@
         </is>
       </c>
       <c r="J255">
-        <v>501</v>
+        <v>114</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035928</t>
+          <t xml:space="preserve">200036025</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-27</t>
+          <t xml:space="preserve">2020-08-30</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aasen 13</t>
+          <t xml:space="preserve">Kildestræde 18</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402857</t>
+          <t xml:space="preserve">5402389</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="J256">
-        <v>210</v>
+        <v>963</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036023</t>
+          <t xml:space="preserve">200036026</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19241,17 +19241,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aasen 49A</t>
+          <t xml:space="preserve">Morbærstien 2</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402786</t>
+          <t xml:space="preserve">5407947</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -19260,21 +19260,21 @@
         </is>
       </c>
       <c r="J257">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036025</t>
+          <t xml:space="preserve">200036173</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-30</t>
+          <t xml:space="preserve">2020-08-31</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,17 +19316,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildestræde 18</t>
+          <t xml:space="preserve">Sagavej 2</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402389</t>
+          <t xml:space="preserve">5411692</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -19335,21 +19335,21 @@
         </is>
       </c>
       <c r="J258">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036026</t>
+          <t xml:space="preserve">200036205</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-30</t>
+          <t xml:space="preserve">2020-09-01</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,17 +19391,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morbærstien 2</t>
+          <t xml:space="preserve">Brænderigænget 10</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407947</t>
+          <t xml:space="preserve">5413395</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -19410,21 +19410,21 @@
         </is>
       </c>
       <c r="J259">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036173</t>
+          <t xml:space="preserve">200036309</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-31</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sagavej 2</t>
+          <t xml:space="preserve">Ullasvej 17</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,30 +19476,30 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411692</t>
+          <t xml:space="preserve">5411642</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J260">
-        <v>956</v>
+        <v>1177</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036205</t>
+          <t xml:space="preserve">200036366</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-01</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,35 +19541,35 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brænderigænget 10</t>
+          <t xml:space="preserve">Ullasvej 23</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413395</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J261">
-        <v>300</v>
+        <v>2517</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036309</t>
+          <t xml:space="preserve">200036384</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -19616,40 +19616,40 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 17</t>
+          <t xml:space="preserve">Borgergade 4</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411642</t>
+          <t xml:space="preserve">5413433</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J262">
-        <v>1177</v>
+        <v>336</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036366</t>
+          <t xml:space="preserve">200036397</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-09-03</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,40 +19691,40 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 23</t>
+          <t xml:space="preserve">Damgade 10B</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5402452</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J263">
-        <v>2517</v>
+        <v>317</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036384</t>
+          <t xml:space="preserve">200036509</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-09-06</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,17 +19766,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 4</t>
+          <t xml:space="preserve">Havnen 9</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413433</t>
+          <t xml:space="preserve">5403146</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,11 +19785,11 @@
         </is>
       </c>
       <c r="J264">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036397</t>
+          <t xml:space="preserve">200036610</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-03</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damgade 10B</t>
+          <t xml:space="preserve">Munkegade 18A</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402452</t>
+          <t xml:space="preserve">5402005</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036509</t>
+          <t xml:space="preserve">200036613</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-06</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 9</t>
+          <t xml:space="preserve">Paradisvej 7</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403146</t>
+          <t xml:space="preserve">5403240</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,11 +19935,11 @@
         </is>
       </c>
       <c r="J266">
-        <v>308</v>
+        <v>67</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036610</t>
+          <t xml:space="preserve">200036624</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19991,17 +19991,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkegade 18A</t>
+          <t xml:space="preserve">Damgade 13A</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402005</t>
+          <t xml:space="preserve">5396613</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,11 +20010,11 @@
         </is>
       </c>
       <c r="J267">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036613</t>
+          <t xml:space="preserve">200036761</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2020-09-09</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,17 +20066,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 7</t>
+          <t xml:space="preserve">Lille Madsegade 114</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403240</t>
+          <t xml:space="preserve">5407230</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,21 +20085,21 @@
         </is>
       </c>
       <c r="J268">
-        <v>67</v>
+        <v>734</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036624</t>
+          <t xml:space="preserve">200037141</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,17 +20141,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damgade 13A</t>
+          <t xml:space="preserve">Sandemandsvej 1A</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5396613</t>
+          <t xml:space="preserve">288308, 288309</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,21 +20160,21 @@
         </is>
       </c>
       <c r="J269">
-        <v>152</v>
+        <v>2282</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036761</t>
+          <t xml:space="preserve">200037152</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-09</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Madsegade 114</t>
+          <t xml:space="preserve">Sandemandsvej 4B</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407230</t>
+          <t xml:space="preserve">5147263</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -20235,11 +20235,11 @@
         </is>
       </c>
       <c r="J270">
-        <v>734</v>
+        <v>1243</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037141</t>
+          <t xml:space="preserve">200037111</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandemandsvej 1A</t>
+          <t xml:space="preserve">Smedeløkken 5</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">288308, 288309</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -20310,16 +20310,16 @@
         </is>
       </c>
       <c r="J271">
-        <v>2282</v>
+        <v>2460</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037152</t>
+          <t xml:space="preserve">200037100</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -20366,40 +20366,40 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandemandsvej 4B</t>
+          <t xml:space="preserve">Åbogade 7</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5147263</t>
+          <t xml:space="preserve">5157951</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J272">
-        <v>1243</v>
+        <v>200</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037111</t>
+          <t xml:space="preserve">200037564</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-09-21</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,17 +20441,17 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeløkken 5</t>
+          <t xml:space="preserve">Eskildsgade 4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">5396434</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -20460,21 +20460,21 @@
         </is>
       </c>
       <c r="J273">
-        <v>2460</v>
+        <v>181</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037100</t>
+          <t xml:space="preserve">200037894</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-09-27</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbogade 7</t>
+          <t xml:space="preserve">Grønningen 10</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5157951</t>
+          <t xml:space="preserve">5397915</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J274">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037564</t>
+          <t xml:space="preserve">200037930</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-21</t>
+          <t xml:space="preserve">2020-09-27</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,30 +20591,30 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskildsgade 4</t>
+          <t xml:space="preserve">Vestermarievej 48</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5396434</t>
+          <t xml:space="preserve">5151294</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J275">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037894</t>
+          <t xml:space="preserve">200038213</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-27</t>
+          <t xml:space="preserve">2020-09-30</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,17 +20666,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 10</t>
+          <t xml:space="preserve">Fabriksvej 20A</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397915</t>
+          <t xml:space="preserve">5407924</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,21 +20685,21 @@
         </is>
       </c>
       <c r="J276">
-        <v>79</v>
+        <v>612</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037930</t>
+          <t xml:space="preserve">200038276</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-27</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarievej 48</t>
+          <t xml:space="preserve">Hedebovej 7</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,30 +20751,30 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5151294</t>
+          <t xml:space="preserve">5146500</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J277">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038213</t>
+          <t xml:space="preserve">100185205</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-30</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 20A</t>
+          <t xml:space="preserve">Kanegårdsvej 27</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407924</t>
+          <t xml:space="preserve">8341312</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -20835,11 +20835,11 @@
         </is>
       </c>
       <c r="J278">
-        <v>612</v>
+        <v>90</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038276</t>
+          <t xml:space="preserve">200038279</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedebovej 7</t>
+          <t xml:space="preserve">Snorrebakken 62</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146500</t>
+          <t xml:space="preserve">5146401</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -20910,11 +20910,11 @@
         </is>
       </c>
       <c r="J279">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">100185205</t>
+          <t xml:space="preserve">200038280</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanegårdsvej 27</t>
+          <t xml:space="preserve">Snorrebakken 64</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341312</t>
+          <t xml:space="preserve">5146403</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -20985,11 +20985,11 @@
         </is>
       </c>
       <c r="J280">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038279</t>
+          <t xml:space="preserve">100185200</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 62</t>
+          <t xml:space="preserve">Snorrebakken 66</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146401</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -21060,11 +21060,11 @@
         </is>
       </c>
       <c r="J281">
-        <v>118</v>
+        <v>1972</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038280</t>
+          <t xml:space="preserve">200038288</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 64</t>
+          <t xml:space="preserve">Strandvejen 198</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21126,20 +21126,20 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146403</t>
+          <t xml:space="preserve">8341362</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J282">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">100185200</t>
+          <t xml:space="preserve">200038275</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21191,17 +21191,17 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 66</t>
+          <t xml:space="preserve">Gudhjemvej 107</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">5158331</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -21210,21 +21210,21 @@
         </is>
       </c>
       <c r="J283">
-        <v>1972</v>
+        <v>278</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038288</t>
+          <t xml:space="preserve">200038401</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2020-10-04</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,40 +21266,40 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 198</t>
+          <t xml:space="preserve">Jernbanevej 2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341362</t>
+          <t xml:space="preserve">5151884</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038275</t>
+          <t xml:space="preserve">200038460</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,17 +21341,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gudhjemvej 107</t>
+          <t xml:space="preserve">Limensgaden 5</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158331</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -21360,21 +21360,21 @@
         </is>
       </c>
       <c r="J285">
-        <v>278</v>
+        <v>87</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038401</t>
+          <t xml:space="preserve">200038484</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-04</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,17 +21416,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 2</t>
+          <t xml:space="preserve">Torvegade 12</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5151884</t>
+          <t xml:space="preserve">5161251</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -21435,11 +21435,11 @@
         </is>
       </c>
       <c r="J286">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038460</t>
+          <t xml:space="preserve">200038521</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21491,17 +21491,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Limensgaden 5</t>
+          <t xml:space="preserve">Vestergade 1</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">5398282</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -21510,21 +21510,21 @@
         </is>
       </c>
       <c r="J287">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038484</t>
+          <t xml:space="preserve">200038706</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-05</t>
+          <t xml:space="preserve">2020-10-07</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,30 +21566,30 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 12</t>
+          <t xml:space="preserve">Vestergade 3</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5161251</t>
+          <t xml:space="preserve">5398282</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J288">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038521</t>
+          <t xml:space="preserve">200038704</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-05</t>
+          <t xml:space="preserve">2020-10-07</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,17 +21641,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 1</t>
+          <t xml:space="preserve">Sydskovvej 2</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398282</t>
+          <t xml:space="preserve">288458, 288459</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -21660,21 +21660,21 @@
         </is>
       </c>
       <c r="J289">
-        <v>208</v>
+        <v>1231</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038706</t>
+          <t xml:space="preserve">200038748</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-07</t>
+          <t xml:space="preserve">2020-10-08</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,30 +21716,30 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 3</t>
+          <t xml:space="preserve">Jernbanegade 33</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398282</t>
+          <t xml:space="preserve">5397250</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J290">
-        <v>87</v>
+        <v>300</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038704</t>
+          <t xml:space="preserve">100187070</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-07</t>
+          <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,17 +21791,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydskovvej 2</t>
+          <t xml:space="preserve">Kannikeengen 14</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">288458, 288459</t>
+          <t xml:space="preserve">5152206</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -21810,21 +21810,21 @@
         </is>
       </c>
       <c r="J291">
-        <v>1231</v>
+        <v>116</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038748</t>
+          <t xml:space="preserve">100187059</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-08</t>
+          <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 33</t>
+          <t xml:space="preserve">Møllebakken 3A</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397250</t>
+          <t xml:space="preserve">9806294</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -21885,11 +21885,11 @@
         </is>
       </c>
       <c r="J292">
-        <v>300</v>
+        <v>209</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">100187070</t>
+          <t xml:space="preserve">200038836</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21941,17 +21941,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kannikeengen 14</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152206</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -21960,21 +21960,21 @@
         </is>
       </c>
       <c r="J293">
-        <v>116</v>
+        <v>3649</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">100187059</t>
+          <t xml:space="preserve">200038976</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-11</t>
+          <t xml:space="preserve">2020-10-12</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,17 +22016,17 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 3A</t>
+          <t xml:space="preserve">Søndervænget 4</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">9806294</t>
+          <t xml:space="preserve">5398447</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -22035,11 +22035,11 @@
         </is>
       </c>
       <c r="J294">
-        <v>209</v>
+        <v>310</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038836</t>
+          <t xml:space="preserve">200038941</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-11</t>
+          <t xml:space="preserve">2020-10-12</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Fabriksvej 31</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22101,30 +22101,30 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">7636485</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J295">
-        <v>3649</v>
+        <v>991</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038976</t>
+          <t xml:space="preserve">200039035</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-12</t>
+          <t xml:space="preserve">2020-10-13</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndervænget 4</t>
+          <t xml:space="preserve">Ndr. Strandvej 31</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398447</t>
+          <t xml:space="preserve">7117984</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -22185,11 +22185,11 @@
         </is>
       </c>
       <c r="J296">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038941</t>
+          <t xml:space="preserve">200039001</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-12</t>
+          <t xml:space="preserve">2020-10-13</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 31</t>
+          <t xml:space="preserve">Smedegårdsvej 34</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22251,20 +22251,20 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">7636485</t>
+          <t xml:space="preserve">9806273</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>991</v>
+        <v>250</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039035</t>
+          <t xml:space="preserve">200039020</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22316,35 +22316,35 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr. Strandvej 31</t>
+          <t xml:space="preserve">Smedegårdsvej 34</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">7117984</t>
+          <t xml:space="preserve">9806273</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J298">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039001</t>
+          <t xml:space="preserve">200039020</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegårdsvej 34</t>
+          <t xml:space="preserve">Dr Kabells Vej 24A</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">9806273</t>
+          <t xml:space="preserve">5409944</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -22410,11 +22410,11 @@
         </is>
       </c>
       <c r="J299">
-        <v>250</v>
+        <v>468</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039020</t>
+          <t xml:space="preserve">200039135</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-13</t>
+          <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -22466,40 +22466,40 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegårdsvej 34</t>
+          <t xml:space="preserve">Pihls Alle 32</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">9806273</t>
+          <t xml:space="preserve">5162734</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>241</v>
+        <v>360</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039020</t>
+          <t xml:space="preserve">200039090</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-13</t>
+          <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr Kabells Vej 24A</t>
+          <t xml:space="preserve">Pingels Alle 1</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409944</t>
+          <t xml:space="preserve">7255632</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -22560,11 +22560,11 @@
         </is>
       </c>
       <c r="J301">
-        <v>468</v>
+        <v>2346</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039135</t>
+          <t xml:space="preserve">200039139</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,17 +22616,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pihls Alle 32</t>
+          <t xml:space="preserve">Fælledvej 98</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162734</t>
+          <t xml:space="preserve">5401635</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -22635,11 +22635,11 @@
         </is>
       </c>
       <c r="J302">
-        <v>360</v>
+        <v>73</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039090</t>
+          <t xml:space="preserve">200039142</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-14</t>
+          <t xml:space="preserve">2020-10-15</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pingels Alle 1</t>
+          <t xml:space="preserve">Møllevej 6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255632</t>
+          <t xml:space="preserve">5149004</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -22710,21 +22710,21 @@
         </is>
       </c>
       <c r="J303">
-        <v>2346</v>
+        <v>212</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039139</t>
+          <t xml:space="preserve">200039272</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-14</t>
+          <t xml:space="preserve">2020-10-18</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 98</t>
+          <t xml:space="preserve">Byvangen 4</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401635</t>
+          <t xml:space="preserve">7011084</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -22785,11 +22785,11 @@
         </is>
       </c>
       <c r="J304">
-        <v>73</v>
+        <v>237</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039142</t>
+          <t xml:space="preserve">200039411</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-15</t>
+          <t xml:space="preserve">2020-10-19</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22841,17 +22841,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 6</t>
+          <t xml:space="preserve">Industrivej 6</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5149004</t>
+          <t xml:space="preserve">5162690</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -22860,11 +22860,11 @@
         </is>
       </c>
       <c r="J305">
-        <v>212</v>
+        <v>619</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039272</t>
+          <t xml:space="preserve">200039409</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-18</t>
+          <t xml:space="preserve">2020-10-19</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22916,17 +22916,17 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvangen 4</t>
+          <t xml:space="preserve">Kildesgårdsvej 1</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">7011084</t>
+          <t xml:space="preserve">5165482</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -22935,11 +22935,11 @@
         </is>
       </c>
       <c r="J306">
-        <v>237</v>
+        <v>395</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039411</t>
+          <t xml:space="preserve">200039408</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22991,30 +22991,30 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 6</t>
+          <t xml:space="preserve">Kirkegade 8</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162690</t>
+          <t xml:space="preserve">5400670</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J307">
-        <v>619</v>
+        <v>141</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039409</t>
+          <t xml:space="preserve">200039667</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-19</t>
+          <t xml:space="preserve">2020-10-24</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildesgårdsvej 1</t>
+          <t xml:space="preserve">Kirkeplads 2</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5165482</t>
+          <t xml:space="preserve">5398315</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -23085,11 +23085,11 @@
         </is>
       </c>
       <c r="J308">
-        <v>395</v>
+        <v>809</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039408</t>
+          <t xml:space="preserve">200039670</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-19</t>
+          <t xml:space="preserve">2020-10-25</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23141,40 +23141,40 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 8</t>
+          <t xml:space="preserve">Møllevænget 1</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400670</t>
+          <t xml:space="preserve">5404249</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J309">
-        <v>141</v>
+        <v>2869</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039667</t>
+          <t xml:space="preserve">200039729</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-24</t>
+          <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23216,17 +23216,17 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkeplads 2</t>
+          <t xml:space="preserve">Storegade 64</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398315</t>
+          <t xml:space="preserve">5400565</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -23235,11 +23235,11 @@
         </is>
       </c>
       <c r="J310">
-        <v>809</v>
+        <v>605</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039670</t>
+          <t xml:space="preserve">200039746</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-25</t>
+          <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23291,17 +23291,17 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 1</t>
+          <t xml:space="preserve">Almindingensvej 23</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404249</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -23310,21 +23310,21 @@
         </is>
       </c>
       <c r="J311">
-        <v>2869</v>
+        <v>423</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039729</t>
+          <t xml:space="preserve">200039893</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-26</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23366,17 +23366,17 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 64</t>
+          <t xml:space="preserve">Curdtslund 2</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400565</t>
+          <t xml:space="preserve">5411643</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -23385,21 +23385,21 @@
         </is>
       </c>
       <c r="J312">
-        <v>605</v>
+        <v>4582</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039746</t>
+          <t xml:space="preserve">200039847</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-26</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23441,17 +23441,17 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Almindingensvej 23</t>
+          <t xml:space="preserve">Helsevej 9</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">5411636</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -23460,16 +23460,16 @@
         </is>
       </c>
       <c r="J313">
-        <v>423</v>
+        <v>293</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039893</t>
+          <t xml:space="preserve">200039828</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curdtslund 2</t>
+          <t xml:space="preserve">Louisenhøj 51</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411643</t>
+          <t xml:space="preserve">5408845</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -23535,11 +23535,11 @@
         </is>
       </c>
       <c r="J314">
-        <v>4582</v>
+        <v>97</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039847</t>
+          <t xml:space="preserve">200039845</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -23591,17 +23591,17 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helsevej 9</t>
+          <t xml:space="preserve">Nygade 40</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411636</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -23610,16 +23610,16 @@
         </is>
       </c>
       <c r="J315">
-        <v>293</v>
+        <v>1368</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039828</t>
+          <t xml:space="preserve">200039896</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Louisenhøj 51</t>
+          <t xml:space="preserve">Paradisvej 6</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">5408845</t>
+          <t xml:space="preserve">5411634</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -23685,11 +23685,11 @@
         </is>
       </c>
       <c r="J316">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039845</t>
+          <t xml:space="preserve">200039822</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23741,17 +23741,17 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 40</t>
+          <t xml:space="preserve">Stenbrudsvej 43</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">8222599</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -23760,16 +23760,16 @@
         </is>
       </c>
       <c r="J317">
-        <v>1368</v>
+        <v>384</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039896</t>
+          <t xml:space="preserve">200039808</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 6</t>
+          <t xml:space="preserve">Store Torv 6A</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411634</t>
+          <t xml:space="preserve">7370629</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -23835,11 +23835,11 @@
         </is>
       </c>
       <c r="J318">
-        <v>337</v>
+        <v>1857</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039822</t>
+          <t xml:space="preserve">200039835</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23891,17 +23891,17 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbrudsvej 43</t>
+          <t xml:space="preserve">Kildesgårdsvej 19</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">8222599</t>
+          <t xml:space="preserve">5164440</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,21 +23910,21 @@
         </is>
       </c>
       <c r="J319">
-        <v>384</v>
+        <v>181</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039808</t>
+          <t xml:space="preserve">200040831</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,17 +23966,17 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Torv 6A</t>
+          <t xml:space="preserve">Otto Bruuns Plads 1</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">7370629</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -23985,21 +23985,21 @@
         </is>
       </c>
       <c r="J320">
-        <v>1857</v>
+        <v>822</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039835</t>
+          <t xml:space="preserve">200040832</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,35 +24041,35 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildesgårdsvej 19</t>
+          <t xml:space="preserve">Stadionvej 4</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164440</t>
+          <t xml:space="preserve">5162695</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J321">
-        <v>181</v>
+        <v>1555</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040831</t>
+          <t xml:space="preserve">200040823</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -24116,30 +24116,30 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otto Bruuns Plads 1</t>
+          <t xml:space="preserve">Stadionvej 4A</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">725293, 5162695</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J322">
-        <v>822</v>
+        <v>440</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040832</t>
+          <t xml:space="preserve">200040823</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24191,30 +24191,30 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 4</t>
+          <t xml:space="preserve">Toftelunden 1A</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162695</t>
+          <t xml:space="preserve">8359771</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J323">
-        <v>1555</v>
+        <v>1439</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040823</t>
+          <t xml:space="preserve">200040821</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24266,35 +24266,35 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 4A</t>
+          <t xml:space="preserve">Toftelunden 5</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">725293, 5162695</t>
+          <t xml:space="preserve">5401681</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J324">
-        <v>440</v>
+        <v>4130</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040823</t>
+          <t xml:space="preserve">200040820</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftelunden 1A</t>
+          <t xml:space="preserve">Kirkegade 4</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359771</t>
+          <t xml:space="preserve">8359765</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -24360,21 +24360,21 @@
         </is>
       </c>
       <c r="J325">
-        <v>1439</v>
+        <v>2569</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040821</t>
+          <t xml:space="preserve">200040860</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">B.K. Consult aps</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-10</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftelunden 5</t>
+          <t xml:space="preserve">Kirkegade 4</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -24426,20 +24426,20 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401681</t>
+          <t xml:space="preserve">8359765</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J326">
-        <v>4130</v>
+        <v>735</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040820</t>
+          <t xml:space="preserve">200040860</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -24449,7 +24449,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-10</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,30 +24491,30 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 4</t>
+          <t xml:space="preserve">Rø Skolevej 6</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359765</t>
+          <t xml:space="preserve">7118089</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J327">
-        <v>2569</v>
+        <v>960</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040860</t>
+          <t xml:space="preserve">200040903</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24566,30 +24566,30 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 4</t>
+          <t xml:space="preserve">Rø Skolevej 8</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359765</t>
+          <t xml:space="preserve">7118089</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J328">
-        <v>735</v>
+        <v>1265</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040860</t>
+          <t xml:space="preserve">200040899</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24641,30 +24641,30 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rø Skolevej 6</t>
+          <t xml:space="preserve">Skovløkken 4</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">7118089</t>
+          <t xml:space="preserve">5164475</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J329">
-        <v>960</v>
+        <v>2346</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040903</t>
+          <t xml:space="preserve">200040869</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -24716,30 +24716,30 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rø Skolevej 8</t>
+          <t xml:space="preserve">Store Torv 6B</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">7118089</t>
+          <t xml:space="preserve">7370629</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J330">
-        <v>1265</v>
+        <v>520</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040899</t>
+          <t xml:space="preserve">200047438</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-03-31</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -24791,17 +24791,17 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovløkken 4</t>
+          <t xml:space="preserve">Skoleparken 9</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164475</t>
+          <t xml:space="preserve">5152219</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -24810,21 +24810,21 @@
         </is>
       </c>
       <c r="J331">
-        <v>2346</v>
+        <v>95</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040869</t>
+          <t xml:space="preserve">100215493</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-04-05</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -24866,40 +24866,40 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Torv 6B</t>
+          <t xml:space="preserve">Skolevej 9</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">7370629</t>
+          <t xml:space="preserve">5152207</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J332">
-        <v>520</v>
+        <v>351</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047438</t>
+          <t xml:space="preserve">200047661</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.K. Consult aps</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-31</t>
+          <t xml:space="preserve">2021-04-05</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -24941,17 +24941,17 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoleparken 9</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152219</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -24960,21 +24960,21 @@
         </is>
       </c>
       <c r="J333">
-        <v>95</v>
+        <v>927</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">100215493</t>
+          <t xml:space="preserve">200048591</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-05</t>
+          <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 9</t>
+          <t xml:space="preserve">Eskildsgade 15</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152207</t>
+          <t xml:space="preserve">5396503</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -25035,21 +25035,21 @@
         </is>
       </c>
       <c r="J334">
-        <v>351</v>
+        <v>820</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047661</t>
+          <t xml:space="preserve">200051846</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-05</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -25091,17 +25091,17 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Grønningen 30</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">8263845</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -25110,21 +25110,21 @@
         </is>
       </c>
       <c r="J335">
-        <v>927</v>
+        <v>3794</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048591</t>
+          <t xml:space="preserve">200051850</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-29</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskildsgade 15</t>
+          <t xml:space="preserve">Klintebovej 16</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -25176,20 +25176,20 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">5396503</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J336">
-        <v>820</v>
+        <v>769</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051846</t>
+          <t xml:space="preserve">200051845</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 30</t>
+          <t xml:space="preserve">Rønnevej 106</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -25251,7 +25251,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263845</t>
+          <t xml:space="preserve">5149826</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -25260,11 +25260,11 @@
         </is>
       </c>
       <c r="J337">
-        <v>3794</v>
+        <v>1532</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051850</t>
+          <t xml:space="preserve">200051851</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -25316,30 +25316,30 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintebovej 16</t>
+          <t xml:space="preserve">Solstien 1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">8348046</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J338">
-        <v>769</v>
+        <v>1915</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051845</t>
+          <t xml:space="preserve">200051849</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -25391,17 +25391,17 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 106</t>
+          <t xml:space="preserve">Vestermarievej 16</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">5149826</t>
+          <t xml:space="preserve">5150673</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -25410,11 +25410,11 @@
         </is>
       </c>
       <c r="J339">
-        <v>1532</v>
+        <v>2393</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051851</t>
+          <t xml:space="preserve">200051848</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -25466,17 +25466,17 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solstien 1</t>
+          <t xml:space="preserve">Kommandanthøjen 2</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348046</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -25485,21 +25485,21 @@
         </is>
       </c>
       <c r="J340">
-        <v>1915</v>
+        <v>699</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051849</t>
+          <t xml:space="preserve">310039658</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+          <t xml:space="preserve">Botjek a/s, Rønne Øst</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2023-05-14</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarievej 16</t>
+          <t xml:space="preserve">Kommandanthøjen 30</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,30 +25551,30 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5150673</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J341">
-        <v>2393</v>
+        <v>459</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051848</t>
+          <t xml:space="preserve">310039650</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+          <t xml:space="preserve">Botjek a/s, Rønne Øst</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2023-05-14</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kommandanthøjen 2</t>
+          <t xml:space="preserve">Kommandanthøjen 42</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25631,15 +25631,15 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J342">
-        <v>699</v>
+        <v>460</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039658</t>
+          <t xml:space="preserve">310039646</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kommandanthøjen 30</t>
+          <t xml:space="preserve">Kommandanthøjen 56</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -25706,15 +25706,15 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J343">
-        <v>459</v>
+        <v>384</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039650</t>
+          <t xml:space="preserve">310039648</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kommandanthøjen 42</t>
+          <t xml:space="preserve">Østre Ringvej 1</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25776,30 +25776,30 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">5146695</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J344">
-        <v>460</v>
+        <v>670</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039646</t>
+          <t xml:space="preserve">311007000</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek a/s, Rønne Øst</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-14</t>
+          <t xml:space="preserve">2023-07-03</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -25841,30 +25841,30 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kommandanthøjen 56</t>
+          <t xml:space="preserve">Pihls Alle 10</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">5163605</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J345">
-        <v>384</v>
+        <v>1710</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039648</t>
+          <t xml:space="preserve">311020824</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-14</t>
+          <t xml:space="preserve">2023-10-07</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Ringvej 1</t>
+          <t xml:space="preserve">Stenbanen 50</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -25926,30 +25926,30 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146695</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J346">
-        <v>670</v>
+        <v>282</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311007000</t>
+          <t xml:space="preserve">311035115</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-03</t>
+          <t xml:space="preserve">2024-01-23</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -25991,40 +25991,40 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pihls Alle 10</t>
+          <t xml:space="preserve">Stenbanen 36</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">5163605</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J347">
-        <v>1710</v>
+        <v>450</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311020824</t>
+          <t xml:space="preserve">311035543</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek a/s, Rønne Øst</t>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-07</t>
+          <t xml:space="preserve">2024-01-27</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26066,40 +26066,40 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbanen 50</t>
+          <t xml:space="preserve">Grønningen 32</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">100063665</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J348">
-        <v>282</v>
+        <v>1227</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311035115</t>
+          <t xml:space="preserve">311048343</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+          <t xml:space="preserve">Botjek, Rønne Øst</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-23</t>
+          <t xml:space="preserve">2024-04-10</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbanen 36</t>
+          <t xml:space="preserve">Snorrebakke Allé 1</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -26151,30 +26151,30 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">100056909</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J349">
-        <v>450</v>
+        <v>1592</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311035543</t>
+          <t xml:space="preserve">311058955</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-27</t>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -26216,40 +26216,40 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 32</t>
+          <t xml:space="preserve">Snorrebakke Allé 3</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063665</t>
+          <t xml:space="preserve">100056909</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J350">
-        <v>1227</v>
+        <v>1592</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">311048343</t>
+          <t xml:space="preserve">311058967</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek, Rønne Øst</t>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04-10</t>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakke Allé 1</t>
+          <t xml:space="preserve">Snorrebakke Allé 5</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J351">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">311058955</t>
+          <t xml:space="preserve">311058958</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -26366,40 +26366,40 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakke Allé 3</t>
+          <t xml:space="preserve">Melstedvej 25A</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">100056909</t>
+          <t xml:space="preserve">725965, 8543660</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J352">
-        <v>1592</v>
+        <v>255</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311058967</t>
+          <t xml:space="preserve">311101751</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-12</t>
+          <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -26441,7 +26441,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakke Allé 5</t>
+          <t xml:space="preserve">Vibegårdsvej 14</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -26451,30 +26451,30 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">100056909</t>
+          <t xml:space="preserve">7006647</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J353">
-        <v>1592</v>
+        <v>638</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t xml:space="preserve">311058958</t>
+          <t xml:space="preserve">311182811</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-12</t>
+          <t xml:space="preserve">2026-06-13</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -26516,50 +26516,50 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melstedvej 25A</t>
+          <t xml:space="preserve">Kæmpestranden 8</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">725965, 8543660</t>
+          <t xml:space="preserve">725180, 5398549</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J354">
-        <v>255</v>
+        <v>1129</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101751</t>
+          <t xml:space="preserve">311244668</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-19</t>
+          <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -26591,17 +26591,17 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibegårdsvej 14</t>
+          <t xml:space="preserve">Rø Skolevej 16</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006647</t>
+          <t xml:space="preserve">725159, 5166867</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -26610,31 +26610,31 @@
         </is>
       </c>
       <c r="J355">
-        <v>638</v>
+        <v>575</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">311182811</t>
+          <t xml:space="preserve">311249329</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+          <t xml:space="preserve">Bodal Energi- &amp; Miljørådgivning</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-13</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -26666,40 +26666,40 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kæmpestranden 8</t>
+          <t xml:space="preserve">Krystalgade 9</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">725180, 5398549</t>
+          <t xml:space="preserve">10160985</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J356">
-        <v>1129</v>
+        <v>3417</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244668</t>
+          <t xml:space="preserve">311283506</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-02</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -26741,40 +26741,40 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rø Skolevej 16</t>
+          <t xml:space="preserve">Skovbrynet 1</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">725159, 5166867</t>
+          <t xml:space="preserve">725208, 5164443</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J357">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249329</t>
+          <t xml:space="preserve">311430366</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodal Energi- &amp; Miljørådgivning</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2030-03-27</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -26801,12 +26801,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Regionskommune</t>
+          <t xml:space="preserve">DVB Parken</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krystalgade 9</t>
+          <t xml:space="preserve">Paradisvej 67</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -26826,20 +26826,20 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">10160985</t>
+          <t xml:space="preserve">291032, 291033</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J358">
-        <v>3417</v>
+        <v>3768</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283506</t>
+          <t xml:space="preserve">311602108</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26849,7 +26849,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -26876,12 +26876,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornholms Regionskommune</t>
+          <t xml:space="preserve">DVB Parken</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -26891,17 +26891,17 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 1</t>
+          <t xml:space="preserve">Paradisvej 11</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">725208, 5164443</t>
+          <t xml:space="preserve">291035, 291036</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -26910,11 +26910,11 @@
         </is>
       </c>
       <c r="J359">
-        <v>586</v>
+        <v>963</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430366</t>
+          <t xml:space="preserve">311602355</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-27</t>
+          <t xml:space="preserve">2032-05-23</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">DVB Parken</t>
+          <t xml:space="preserve">Britta Riis Kofoed-Pihl</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 67</t>
+          <t xml:space="preserve">Fabriksvej 2</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -26976,7 +26976,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">291032, 291033</t>
+          <t xml:space="preserve">290650, 290651, 290652, 290653, 290654, 290655, 290656</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -26985,21 +26985,21 @@
         </is>
       </c>
       <c r="J360">
-        <v>3768</v>
+        <v>858</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602108</t>
+          <t xml:space="preserve">311643803</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">DVB Parken</t>
+          <t xml:space="preserve">Ejerlejlighedsforening Tejn Butikscenter</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -27041,17 +27041,17 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 11</t>
+          <t xml:space="preserve">Ndr. Strandvej 2A</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">291035, 291036</t>
+          <t xml:space="preserve">501210, 501211, 501217, 501213, 501214, 501215, 501216, 5165791</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -27060,11 +27060,11 @@
         </is>
       </c>
       <c r="J361">
-        <v>963</v>
+        <v>1485</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602355</t>
+          <t xml:space="preserve">311664132</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -27074,7 +27074,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-23</t>
+          <t xml:space="preserve">2033-03-03</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -27101,12 +27101,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britta Riis Kofoed-Pihl</t>
+          <t xml:space="preserve">Bornholms Regionskommune</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 2</t>
+          <t xml:space="preserve">Kommandanthøjen 2</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -27126,30 +27126,30 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">290650, 290651, 290652, 290653, 290654, 290655, 290656</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J362">
-        <v>858</v>
+        <v>160</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643803</t>
+          <t xml:space="preserve">311746845</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -27176,12 +27176,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejerlejlighedsforening Tejn Butikscenter</t>
+          <t xml:space="preserve">Bornholms Regionskommune</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -27191,7 +27191,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr. Strandvej 2A</t>
+          <t xml:space="preserve">Rønnevej 3</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -27201,30 +27201,30 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">501210, 501211, 501217, 501213, 501214, 501215, 501216, 5165791</t>
+          <t xml:space="preserve">725184, 5399685</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J363">
-        <v>1485</v>
+        <v>69</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664132</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-03</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -27266,40 +27266,40 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kommandanthøjen 2</t>
+          <t xml:space="preserve">Rønnevej 3</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">725184, 5399685</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J364">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746845</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-21</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -27356,15 +27356,15 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J365">
-        <v>69</v>
+        <v>418</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27431,15 +27431,15 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J366">
-        <v>75</v>
+        <v>691</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27506,15 +27506,15 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J367">
-        <v>418</v>
+        <v>618</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27581,15 +27581,15 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J368">
-        <v>691</v>
+        <v>126</v>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27656,15 +27656,15 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J369">
-        <v>618</v>
+        <v>190</v>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -27731,15 +27731,15 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="J370">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27806,15 +27806,15 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="J371">
-        <v>190</v>
+        <v>694</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878988</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27881,15 +27881,15 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="J372">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27956,15 +27956,15 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J373">
-        <v>694</v>
+        <v>795</v>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -28031,15 +28031,15 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J374">
-        <v>149</v>
+        <v>366</v>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -28091,7 +28091,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 3</t>
+          <t xml:space="preserve">Rønnevej 5</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -28101,20 +28101,20 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">725184, 5399685</t>
+          <t xml:space="preserve">5399685</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J375">
-        <v>795</v>
+        <v>256</v>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878984</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -28166,40 +28166,40 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 3</t>
+          <t xml:space="preserve">Gruset 1</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">725184, 5399685</t>
+          <t xml:space="preserve">725333, 5413941</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J376">
-        <v>366</v>
+        <v>281</v>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311883856</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-28</t>
+          <t xml:space="preserve">2036-02-24</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -28241,40 +28241,40 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 5</t>
+          <t xml:space="preserve">Andr Riis Vej 15</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">5399685</t>
+          <t xml:space="preserve">100683656</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J377">
-        <v>256</v>
+        <v>604</v>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311894233</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-28</t>
+          <t xml:space="preserve">2036-04-15</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -28316,40 +28316,40 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gruset 1</t>
+          <t xml:space="preserve">Hasselvej 7</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">725333, 5413941</t>
+          <t xml:space="preserve">5401678</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J378">
-        <v>281</v>
+        <v>568</v>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883856</t>
+          <t xml:space="preserve">311894229</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-24</t>
+          <t xml:space="preserve">2036-04-15</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -28391,30 +28391,30 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andr Riis Vej 15</t>
+          <t xml:space="preserve">Industrivej 11</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">100683656</t>
+          <t xml:space="preserve">5403877</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J379">
-        <v>604</v>
+        <v>995</v>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894233</t>
+          <t xml:space="preserve">311894227</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -28466,17 +28466,17 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hasselvej 7</t>
+          <t xml:space="preserve">Skoleparken 6</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401678</t>
+          <t xml:space="preserve">5152222</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -28485,21 +28485,21 @@
         </is>
       </c>
       <c r="J380">
-        <v>568</v>
+        <v>122</v>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894229</t>
+          <t xml:space="preserve">311901873</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-15</t>
+          <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -28541,40 +28541,40 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 11</t>
+          <t xml:space="preserve">Snorrebakken 60</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403877</t>
+          <t xml:space="preserve">5146402</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J381">
-        <v>995</v>
+        <v>185</v>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894227</t>
+          <t xml:space="preserve">311911518</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-15</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -28616,7 +28616,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoleparken 6</t>
+          <t xml:space="preserve">Æblehaven 1</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152222</t>
+          <t xml:space="preserve">5396965</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -28635,21 +28635,21 @@
         </is>
       </c>
       <c r="J382">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901873</t>
+          <t xml:space="preserve">311911529</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-18</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 60</t>
+          <t xml:space="preserve">Hedningestræde 6</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -28701,7 +28701,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146402</t>
+          <t xml:space="preserve">5405093</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -28710,21 +28710,21 @@
         </is>
       </c>
       <c r="J383">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911518</t>
+          <t xml:space="preserve">311926581</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -28766,17 +28766,17 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 1</t>
+          <t xml:space="preserve">Kildestræde 14A</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">5396965</t>
+          <t xml:space="preserve">5402422</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -28785,21 +28785,21 @@
         </is>
       </c>
       <c r="J384">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911529</t>
+          <t xml:space="preserve">311927994</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-09-24</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">

--- a/public/exports-from-60-with-coowners/26696348.xlsx
+++ b/public/exports-from-60-with-coowners/26696348.xlsx
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033151</t>
+          <t xml:space="preserve">200033111</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033703</t>
+          <t xml:space="preserve">200033702</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035250</t>
+          <t xml:space="preserve">200035229</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878988</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878984</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -28039,7 +28039,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
